--- a/tools/importer/reports/import-hajj-homepage.report.xlsx
+++ b/tools/importer/reports/import-hajj-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>hajj-homepage</t>
   </si>
   <si>
-    <t>2026-06-24T10:52:00.786Z</t>
+    <t>2026-06-30T08:39:05.533Z</t>
   </si>
   <si>
     <t>Nusuk Hajj Platform</t>
